--- a/excel_templates/用户点赞表.xlsx
+++ b/excel_templates/用户点赞表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,6 +590,141 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>e19abf30-4432-4e3d-9109-44dff614033b</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0af19773-31d9-441b-b645-6388d5e0c75c</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:35:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cdbbc903-c207-442a-83ff-284583c98ddb</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>45211578-f369-4bc7-9a03-996621c08b86</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:35:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8d7c1e1d-e9a5-4466-ae32-051f1b2905cd</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>USR002</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:35:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>02e74cb9-be31-4f9b-8776-010447a54f70</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>USR003</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:35:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>04dcf91b-caf4-4aff-a9df-c1c24fd8d984</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>USR001</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>c064ed1a-8ebc-4d56-a932-f9b467a509ac</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-02-25 09:35:53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
